--- a/app/content/xingxing.xlsx
+++ b/app/content/xingxing.xlsx
@@ -882,7 +882,7 @@
         <v>据理力争</v>
       </c>
       <c r="C2" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D2" t="str">
         <v>把整顿的道理，一条一条摆出来。</v>
@@ -905,7 +905,7 @@
         <v>陈述实情</v>
       </c>
       <c r="C3" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D3" t="str">
         <v>不辩解，只把看到的实情说给他听。</v>
@@ -928,7 +928,7 @@
         <v>态度鲜明</v>
       </c>
       <c r="C4" t="str">
-        <v>威</v>
+        <v>势</v>
       </c>
       <c r="D4" t="str">
         <v>明天会上，第一个表态：队伍不能散。</v>
@@ -951,7 +951,7 @@
         <v>直言无隐</v>
       </c>
       <c r="C5" t="str">
-        <v>威</v>
+        <v>隐</v>
       </c>
       <c r="D5" t="str">
         <v>连他不爱听的，也照实说。</v>
@@ -974,7 +974,7 @@
         <v>顺着乡音</v>
       </c>
       <c r="C6" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D6" t="str">
         <v>学他的湖南腔，把话说到一块去。</v>
@@ -997,7 +997,7 @@
         <v>念念伤员</v>
       </c>
       <c r="C7" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>说祠堂里那些攥着他的手的伤员。</v>
@@ -1020,7 +1020,7 @@
         <v>护着火种</v>
       </c>
       <c r="C8" t="str">
-        <v>利</v>
+        <v>器</v>
       </c>
       <c r="D8" t="str">
         <v>替干部学校争人手、争经费。</v>
@@ -1043,7 +1043,7 @@
         <v>教「人」与「手」</v>
       </c>
       <c r="C9" t="str">
-        <v>情</v>
+        <v>器</v>
       </c>
       <c r="D9" t="str">
         <v>在门板上一撇一捺，写下「人」，再写下「手」。</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>威,理,威,情,理,威,情</v>
+        <v>势,策,势,策,策,势,策</v>
       </c>
       <c r="I2" t="str">
         <v>g_li_shi,g_qing_huo,g_qing_xiang,g_li_zheng,g_wei_zhi,g_li_huo</v>
